--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2045,10 +2045,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129622165</v>
+        <v>136898917</v>
       </c>
       <c r="B13" t="n">
-        <v>58057</v>
+        <v>58169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2056,58 +2056,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>604603</v>
+        <v>604745</v>
       </c>
       <c r="R13" t="n">
-        <v>6979070</v>
+        <v>6978852</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2134,27 +2118,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>10:49</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Kom ifrån söder och fortsatte över myren till skogen på norra sidan tjärnen.</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2180,13 +2149,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129622165</t>
+          <t>https://artportalen.se/Sighting/136898917</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129910129</v>
+        <v>129622165</v>
       </c>
       <c r="B14" t="n">
         <v>58057</v>
@@ -2216,7 +2185,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2224,19 +2193,31 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>604663</v>
+        <v>604603</v>
       </c>
       <c r="R14" t="n">
-        <v>6978951</v>
+        <v>6979070</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2263,27 +2244,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flög runt mig en liten stund inne i skogen. Strulade med inspelning på telefonen därav dålig bild.</t>
+          <t>Kom ifrån söder och fortsatte över myren till skogen på norra sidan tjärnen.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2309,13 +2290,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129910129</t>
+          <t>https://artportalen.se/Sighting/129622165</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130611431</v>
+        <v>129910129</v>
       </c>
       <c r="B15" t="n">
         <v>58057</v>
@@ -2355,21 +2336,17 @@
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>604699</v>
+        <v>604663</v>
       </c>
       <c r="R15" t="n">
-        <v>6978819</v>
+        <v>6978951</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2396,27 +2373,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2025-11-29</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flög över vägen och satt en stund i träd vid vägkanten.</t>
+          <t>Flög runt mig en liten stund inne i skogen. Strulade med inspelning på telefonen därav dålig bild.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2442,58 +2419,70 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130611431</t>
+          <t>https://artportalen.se/Sighting/129910129</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132024871</v>
+        <v>130611431</v>
       </c>
       <c r="B16" t="n">
-        <v>99195</v>
+        <v>58057</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Paljacka, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>604657</v>
+        <v>604699</v>
       </c>
       <c r="R16" t="n">
-        <v>6978979</v>
+        <v>6978819</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2517,17 +2506,27 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>grupp av blommor</t>
+          <t>Flög över vägen och satt en stund i träd vid vägkanten.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2536,7 +2535,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2554,13 +2552,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132024871</t>
+          <t>https://artportalen.se/Sighting/130611431</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132025096</v>
+        <v>132024871</v>
       </c>
       <c r="B17" t="n">
         <v>99195</v>
@@ -2599,10 +2597,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604654</v>
+        <v>604657</v>
       </c>
       <c r="R17" t="n">
-        <v>6978980</v>
+        <v>6978979</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2629,12 +2627,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2666,13 +2664,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132025096</t>
+          <t>https://artportalen.se/Sighting/132024871</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132176963</v>
+        <v>132025096</v>
       </c>
       <c r="B18" t="n">
         <v>99195</v>
@@ -2711,10 +2709,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>604726</v>
+        <v>604654</v>
       </c>
       <c r="R18" t="n">
-        <v>6978857</v>
+        <v>6978980</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2741,17 +2739,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Grupp av plantor.</t>
+          <t>grupp av blommor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2778,13 +2776,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132176963</t>
+          <t>https://artportalen.se/Sighting/132025096</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132177054</v>
+        <v>132176963</v>
       </c>
       <c r="B19" t="n">
         <v>99195</v>
@@ -2823,10 +2821,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>604653</v>
+        <v>604726</v>
       </c>
       <c r="R19" t="n">
-        <v>6978984</v>
+        <v>6978857</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2863,7 +2861,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Grupp av plantor. Totalt 3 grupper som växte i linje upp mot höjden.</t>
+          <t>Grupp av plantor.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2890,13 +2888,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132177054</t>
+          <t>https://artportalen.se/Sighting/132176963</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132867430</v>
+        <v>132177054</v>
       </c>
       <c r="B20" t="n">
         <v>99195</v>
@@ -2935,10 +2933,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>604634</v>
+        <v>604653</v>
       </c>
       <c r="R20" t="n">
-        <v>6978929</v>
+        <v>6978984</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2965,17 +2963,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Grupp av plantor.</t>
+          <t>Grupp av plantor. Totalt 3 grupper som växte i linje upp mot höjden.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3001,6 +2999,118 @@
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132177054</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132867430</v>
+      </c>
+      <c r="B21" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>604634</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6978929</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Grupp av plantor.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132867430</t>
         </is>
@@ -3027,6 +3137,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ21"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2558,38 +2558,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132024871</v>
+        <v>137144454</v>
       </c>
       <c r="B17" t="n">
-        <v>99195</v>
+        <v>58112</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2597,13 +2613,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>604657</v>
+        <v>604626</v>
       </c>
       <c r="R17" t="n">
-        <v>6978979</v>
+        <v>6979003</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2627,17 +2643,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>grupp av blommor</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2646,7 +2657,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2664,13 +2674,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132024871</t>
+          <t>https://artportalen.se/Sighting/137144454</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132025096</v>
+        <v>132024871</v>
       </c>
       <c r="B18" t="n">
         <v>99195</v>
@@ -2709,10 +2719,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>604654</v>
+        <v>604657</v>
       </c>
       <c r="R18" t="n">
-        <v>6978980</v>
+        <v>6978979</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2739,12 +2749,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2776,13 +2786,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132025096</t>
+          <t>https://artportalen.se/Sighting/132024871</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132176963</v>
+        <v>132025096</v>
       </c>
       <c r="B19" t="n">
         <v>99195</v>
@@ -2821,10 +2831,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>604726</v>
+        <v>604654</v>
       </c>
       <c r="R19" t="n">
-        <v>6978857</v>
+        <v>6978980</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2851,17 +2861,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Grupp av plantor.</t>
+          <t>grupp av blommor</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2888,13 +2898,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132176963</t>
+          <t>https://artportalen.se/Sighting/132025096</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132177054</v>
+        <v>132176963</v>
       </c>
       <c r="B20" t="n">
         <v>99195</v>
@@ -2933,10 +2943,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>604653</v>
+        <v>604726</v>
       </c>
       <c r="R20" t="n">
-        <v>6978984</v>
+        <v>6978857</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2973,7 +2983,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Grupp av plantor. Totalt 3 grupper som växte i linje upp mot höjden.</t>
+          <t>Grupp av plantor.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3000,13 +3010,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132177054</t>
+          <t>https://artportalen.se/Sighting/132176963</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132867430</v>
+        <v>132177054</v>
       </c>
       <c r="B21" t="n">
         <v>99195</v>
@@ -3045,10 +3055,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>604634</v>
+        <v>604653</v>
       </c>
       <c r="R21" t="n">
-        <v>6978929</v>
+        <v>6978984</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3075,17 +3085,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Grupp av plantor.</t>
+          <t>Grupp av plantor. Totalt 3 grupper som växte i linje upp mot höjden.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3111,6 +3121,118 @@
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132177054</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132867430</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Paljacka, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>604634</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6978929</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Grupp av plantor.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Fatima Boukarchid</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132867430</t>
         </is>
@@ -3138,6 +3260,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -2048,7 +2048,7 @@
         <v>136898917</v>
       </c>
       <c r="B13" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>137144454</v>
       </c>
       <c r="B17" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -2048,7 +2048,7 @@
         <v>136898917</v>
       </c>
       <c r="B13" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>137144454</v>
       </c>
       <c r="B17" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -2591,21 +2591,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -2048,7 +2048,7 @@
         <v>136898917</v>
       </c>
       <c r="B13" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>137144454</v>
       </c>
       <c r="B17" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -2048,7 +2048,7 @@
         <v>136898917</v>
       </c>
       <c r="B13" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>137144454</v>
       </c>
       <c r="B17" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -2048,7 +2048,7 @@
         <v>136898917</v>
       </c>
       <c r="B13" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         <v>137144454</v>
       </c>
       <c r="B17" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 26341-2025 artfynd.xlsx
+++ b/artfynd/A 26341-2025 artfynd.xlsx
@@ -2561,7 +2561,7 @@
         <v>137144454</v>
       </c>
       <c r="B17" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
